--- a/sample_data/tests/04 - Logsheet for losses measurement (winding resistance).xlsx
+++ b/sample_data/tests/04 - Logsheet for losses measurement (winding resistance).xlsx
@@ -7,17 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Losses logsheet (resistance)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Winding Resistance and Loss" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="RS_SERIES">'Losses logsheet (resistance)'!$B$3</definedName>
-    <definedName name="RS_SAMPLE">'Losses logsheet (resistance)'!$E$3</definedName>
-    <definedName name="RS_DATE_BT">'Losses logsheet (resistance)'!$B$4</definedName>
-    <definedName name="RS_DATE_AT">'Losses logsheet (resistance)'!$E$4</definedName>
-    <definedName name="RS_OIL_TOP_0">'Losses logsheet (resistance)'!$B$5</definedName>
-    <definedName name="RS_OIL_TOP_1">'Losses logsheet (resistance)'!$E$5</definedName>
-    <definedName name="RS_OIL_BOT_0">'Losses logsheet (resistance)'!$B$6</definedName>
-    <definedName name="RS_OIL_BOT_1">'Losses logsheet (resistance)'!$E$6</definedName>
+    <definedName name="RS2_SERIES">'Winding Resistance and Loss'!$D$6</definedName>
+    <definedName name="RS2_DATE_BT">'Winding Resistance and Loss'!$J$6</definedName>
+    <definedName name="RS2_SAMPLE">'Winding Resistance and Loss'!$D$7</definedName>
+    <definedName name="RS2_DATE_AT">'Winding Resistance and Loss'!$J$7</definedName>
+    <definedName name="RS2_SERIAL">'Winding Resistance and Loss'!$D$8</definedName>
+    <definedName name="RS2_KVA">'Winding Resistance and Loss'!$J$8</definedName>
+    <definedName name="RS2_CUSTOMER">'Winding Resistance and Loss'!$D$9</definedName>
+    <definedName name="RS2_MATERIAL">'Winding Resistance and Loss'!$J$9</definedName>
+    <definedName name="RS2_MANUFACTURER">'Winding Resistance and Loss'!$D$10</definedName>
+    <definedName name="RS2_RATED_V">'Winding Resistance and Loss'!$J$10</definedName>
+    <definedName name="RS2_OIL_TOP_0">'Winding Resistance and Loss'!$E$13</definedName>
+    <definedName name="RS2_OIL_TOP_1">'Winding Resistance and Loss'!$I$13</definedName>
+    <definedName name="RS2_OIL_BOT_0">'Winding Resistance and Loss'!$E$14</definedName>
+    <definedName name="RS2_OIL_BOT_1">'Winding Resistance and Loss'!$I$14</definedName>
+    <definedName name="RS2_SIG_CUSTOMER">'Winding Resistance and Loss'!$A$29</definedName>
+    <definedName name="RS2_SIG_ENGINEER">'Winding Resistance and Loss'!$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,8 +33,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,19 +45,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="13"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="6"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="0056667F"/>
+      <color rgb="001C3D6E"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="0056667F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -56,7 +90,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEA"/>
+        <fgColor rgb="00EAF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -64,8 +103,13 @@
         <fgColor rgb="00DFE7F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -88,6 +132,50 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA8BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA8BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA8BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA8BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA8BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="009AA8BD"/>
       </left>
@@ -124,23 +212,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,277 +632,655 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10.5" customWidth="1" min="1" max="1"/>
+    <col width="10.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="6" max="6"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="10.5" customWidth="1" min="8" max="8"/>
+    <col width="10.5" customWidth="1" min="9" max="9"/>
+    <col width="10.5" customWidth="1" min="10" max="10"/>
+    <col width="10.5" customWidth="1" min="11" max="11"/>
+    <col width="10.5" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" hidden="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Losses logsheet (resistance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Aletheia template resistance v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CPRI Short Circuit Laboratory - form: Aletheia template resistance (version 1). Fill the yellow cells only; do not move or rename them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Fill in the yellow cells as on the paper logsheet. Grey cells are printed text or are calculated; they are locked. Choose from the list where a cell offers one; readings must be numbers and dates must be dates (dd-mm-yyyy). Leave a cell empty if the value is not on the sheet: it is recorded as NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Test series no. (as written)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+          <t>SHORT CIRCUIT LABORATORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>LOG-SHEET FOR LOSS MEASUREMENT ON TRANSFORMER: Measurement of Resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Test Series No</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>25T1656</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Sample code no. (as written)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Before STC test : Date</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="11" t="n">
+        <v>45959</v>
+      </c>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Sample no</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>HVD25S0847</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Date, before SC</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>29-10-2025</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Date, after SC</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>04-11-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Top oil before (C)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Top oil after (C)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Bottom oil before (C)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Bottom oil after (C)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>After STC test : Date</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="11" t="n">
+        <v>45965</v>
+      </c>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Serial no.</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Rated kVA</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Winding resistance (HV ohm, LV milli-ohm)</t>
-        </is>
-      </c>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Winding Material: Copper / Aluminium</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="9" t="n"/>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Tap / winding</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Before short circuit</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>After short circuit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>BT R1</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>BT R2</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>BT R3</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>AT R1</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>AT R2</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>AT R3</t>
-        </is>
-      </c>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Rated voltage (HV / LV)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>3.9736</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>3.9558</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>3.969</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>3.989</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>3.9734</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>3.9864</v>
-      </c>
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Measurement of Resistance</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Before STC test</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>After STC test</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>4.2028</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>4.1822</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>4.1874</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>4.1988</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>4.2092</v>
-      </c>
+          <t>Temperature top oil - °C</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>Temperature bottom oil - °C</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="12" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Resistance of H.V. winding in Ohms / milli-Ohms / micro-Ohms</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Tap Pos.</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Voltage ratio</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Before STC Test</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>After STC Test</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>1U1V</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>1V1W</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>1W1U</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1U1V </t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1V1W </t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1W1U </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="18" t="n">
+        <v>3.9736</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>3.9558</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>3.969</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>3.989</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>3.9734</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>3.9864</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="18" t="n">
+        <v>4.2028</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>4.1822</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>4.1874</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>4.1988</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>4.2092</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="18" t="n">
         <v>3.5476</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="D20" s="18" t="n">
         <v>3.5398</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="E20" s="18" t="n">
         <v>3.5458</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F20" s="18" t="n">
         <v>3.5612</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G20" s="18" t="n">
         <v>3.554</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H20" s="18" t="n">
         <v>3.5622</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Resistance of L.V. winding in Ohms / milli-Ohms / micro-Ohms</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Before STC Test</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>After STC Test</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>2u2v</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>2v2w</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>2w2u</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2u2v </t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2v2w </t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2w2u </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
         <v>3.8716</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="B25" s="18" t="n">
         <v>3.865</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="C25" s="18" t="n">
         <v>3.9074</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="D25" s="18" t="n">
         <v>3.897</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="E25" s="18" t="n">
         <v>3.8844</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="F25" s="18" t="n">
         <v>3.9248</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Customer's Signature</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>APPROVED BY:          Document: FORMS &amp; FORMATS   SECTION : 56   PAGE NO. 1 OF 1   ISSUE NO. 01   REVISION NO.: 00   DATE : 01.06.2019</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="B10:D10"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <mergeCells count="45">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="G30:L30"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
+  <dataValidations count="20">
+    <dataValidation sqref="J6:L6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a date (dd-mm-yyyy)" type="date" operator="greaterThanOrEqual">
+      <formula1>36526</formula1>
+    </dataValidation>
+    <dataValidation sqref="J7:L7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a date (dd-mm-yyyy)" type="date" operator="greaterThanOrEqual">
+      <formula1>36526</formula1>
+    </dataValidation>
+    <dataValidation sqref="J8:L8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (Rated kVA)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="J9:L9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Choose one of the listed values" type="list" errorStyle="stop">
+      <formula1>"Copper,Aluminium"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E13:H13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number between -20 and 150 (Temperature top oil - °C (Before STC test))" type="decimal" operator="between">
+      <formula1>-20</formula1>
+      <formula2>150</formula2>
+    </dataValidation>
+    <dataValidation sqref="I13:L13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number between -20 and 150 (Temperature top oil - °C (After STC test))" type="decimal" operator="between">
+      <formula1>-20</formula1>
+      <formula2>150</formula2>
+    </dataValidation>
+    <dataValidation sqref="E14:H14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number between -20 and 150 (Temperature bottom oil - °C (Before STC test))" type="decimal" operator="between">
+      <formula1>-20</formula1>
+      <formula2>150</formula2>
+    </dataValidation>
+    <dataValidation sqref="I14:L14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number between -20 and 150 (Temperature bottom oil - °C (After STC test))" type="decimal" operator="between">
+      <formula1>-20</formula1>
+      <formula2>150</formula2>
+    </dataValidation>
+    <dataValidation sqref="C18:C20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (1U1V)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D18:D20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (1V1W)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E18:E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (1W1U)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="F18:F20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (1U1V )" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="G18:G20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (1V1W )" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="H18:H20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (1W1U )" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="A25:A27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (2u2v)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B25:B27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (2v2w)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C25:C27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (2w2u)" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D25:D27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (2u2v )" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E25:E27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (2v2w )" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="F25:F27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a number (2w2u )" type="decimal" operator="between">
+      <formula1>-1000000000.0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>